--- a/AAII_Financials/Quarterly/SSLZY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSLZY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
   <si>
     <t>SSLZY</t>
   </si>
@@ -656,280 +656,293 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44196</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44012</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43830</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43646</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43465</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43281</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43100</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>42916</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>42735</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>42551</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>42369</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>42185</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2977000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3057000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4144000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3843000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2725000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2112000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1784000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1728000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2143000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2043000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2046000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1727000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1692000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1506000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1403000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1191000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1181000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1261000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2150000</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1830000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1837000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1990000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1912000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1499000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1485000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1398000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1245000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1457000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1241000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1149000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1162000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1253000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1066000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1069000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1055000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1001000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>882000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1570000</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1147000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1220000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2154000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1931000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1226000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>627000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>386000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>483000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>686000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>802000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>897000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>565000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>439000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>440000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>334000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>136000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>180000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>379000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>580000</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -951,67 +964,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E12" s="3">
         <v>49000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>45000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>103000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>85000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>41000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>34000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>25000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>75000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>28000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>60000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>45000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>41000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>53000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>91000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>47000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>36000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>152000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>154000</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1069,67 +1086,73 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E14" s="3">
         <v>24000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>320000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>39000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>68000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>8000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>134000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>755000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>52000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>25000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>100000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>76000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-34000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>951000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>44000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1477000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2854000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>2289000</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1148,20 +1171,20 @@
       <c r="H15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J15" s="3">
         <v>1000</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3" t="s">
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3000</v>
-      </c>
-      <c r="M15" s="3">
-        <v>1000</v>
       </c>
       <c r="N15" s="3">
         <v>1000</v>
@@ -1176,19 +1199,22 @@
         <v>1000</v>
       </c>
       <c r="R15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S15" s="3">
         <v>4000</v>
-      </c>
-      <c r="S15" s="3">
-        <v>1000</v>
       </c>
       <c r="T15" s="3">
         <v>1000</v>
       </c>
-      <c r="U15" s="3" t="s">
+      <c r="U15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V15" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1207,126 +1233,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2134000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2081000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2826000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2213000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1999000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1633000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1699000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2119000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1715000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1453000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1275000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1392000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1535000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2248000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1286000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2793000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3953000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1087000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3834000</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>843000</v>
+      </c>
+      <c r="E18" s="3">
         <v>976000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1318000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1630000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>726000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>479000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>85000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-391000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>428000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>590000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>771000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>335000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>157000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-742000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>117000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1602000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2772000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>174000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1684000</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1348,8 +1381,9 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1407,67 +1441,73 @@
       <c r="U20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>799000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1927000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1359000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2483000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>741000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1093000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>128000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>95000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>510000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1050000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>782000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>663000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>203000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-394000</v>
       </c>
-      <c r="Q21" s="3" t="s">
+      <c r="R21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1203000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2731000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>550000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1554000</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1525,126 +1565,135 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>843000</v>
+      </c>
+      <c r="E23" s="3">
         <v>976000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1318000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1630000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>726000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>479000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>85000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-391000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>428000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>590000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>771000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>335000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>157000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-742000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>117000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1602000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2772000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>174000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1684000</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>217000</v>
+      </c>
+      <c r="E24" s="3">
         <v>186000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>373000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>463000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>422000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>125000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>153000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-102000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>142000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>202000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>245000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>231000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>11000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-236000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>60000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-498000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-789000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>144000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-543000</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1702,126 +1751,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>626000</v>
+      </c>
+      <c r="E26" s="3">
         <v>790000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>945000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1167000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>304000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>354000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-68000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-289000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>286000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>388000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>526000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>104000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>146000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-506000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>57000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1104000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1983000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>30000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>626000</v>
+      </c>
+      <c r="E27" s="3">
         <v>790000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>945000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1167000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>304000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>354000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-68000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-289000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>286000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>388000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>526000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>104000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>146000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-506000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>57000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1104000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1983000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>30000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1879,8 +1937,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1938,8 +1999,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1997,8 +2061,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2056,8 +2123,11 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2115,67 +2185,73 @@
       <c r="U32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>626000</v>
+      </c>
+      <c r="E33" s="3">
         <v>790000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>945000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1167000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>304000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>354000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-68000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-289000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>286000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>388000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>526000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>104000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>146000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-506000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>57000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1104000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1983000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>30000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2233,131 +2309,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>626000</v>
+      </c>
+      <c r="E35" s="3">
         <v>790000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>945000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1167000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>304000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>354000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-68000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-289000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>286000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>388000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>526000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>104000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>146000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-506000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>57000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1104000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1983000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>30000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44196</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44012</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43830</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43646</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43465</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43281</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43100</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>42916</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>42735</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>42551</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>42369</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>42185</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2379,8 +2464,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2402,515 +2488,540 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1875000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1840000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2352000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3279000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2976000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2417000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1319000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1262000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1067000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1215000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1316000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1492000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1231000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2226000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2026000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1034000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1343000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>399000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>775000</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>404000</v>
+      </c>
+      <c r="E42" s="3">
         <v>91000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>109000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>85000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>7000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>29000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>25000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>195000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>14000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>28000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>14000</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>17000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>7000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>651000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>66000</v>
       </c>
     </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>915000</v>
+      </c>
+      <c r="E43" s="3">
         <v>810000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>843000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>851000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>995000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>703000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>583000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>540000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>577000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>423000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>562000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>451000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>447000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>370000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>382000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>532000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>477000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>650000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>690000</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>442000</v>
+      </c>
+      <c r="E44" s="3">
         <v>455000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>443000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>470000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>406000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>294000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>288000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>284000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>301000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>304000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>288000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>252000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>266000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>284000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>321000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>379000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>360000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>526000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>443000</v>
       </c>
     </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>711000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1331000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1381000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1333000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>367000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>281000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>477000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>25000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>40000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>32000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>293000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>28000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>32000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>214000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>45000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>448000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>86000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>91000</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4347000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4527000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5128000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6018000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4751000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3696000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2696000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2136000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2180000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1966000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2226000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2502000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1972000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2929000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2950000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1991000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2125000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1662000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2065000</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>712000</v>
+      </c>
+      <c r="E47" s="3">
         <v>693000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>660000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>693000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>749000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>510000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>543000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>959000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>172000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>157000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>219000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>82000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>177000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>197000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>213000</v>
-      </c>
-      <c r="R47" s="3">
-        <v>233000</v>
       </c>
       <c r="S47" s="3">
         <v>233000</v>
       </c>
       <c r="T47" s="3">
+        <v>233000</v>
+      </c>
+      <c r="U47" s="3">
         <v>287000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>273000</v>
       </c>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>21972000</v>
+      </c>
+      <c r="E48" s="3">
         <v>20627000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20494000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20297000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21647000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>12568000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>12991000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12796000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12806000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12715000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12383000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9673000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10121000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10169000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11028000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11710000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13105000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21096000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>19795000</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1190000</v>
+        <v>1251000</v>
       </c>
       <c r="E49" s="3">
         <v>1190000</v>
       </c>
       <c r="F49" s="3">
+        <v>1190000</v>
+      </c>
+      <c r="G49" s="3">
         <v>1336000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1463000</v>
-      </c>
-      <c r="H49" s="3">
-        <v>383000</v>
       </c>
       <c r="I49" s="3">
         <v>383000</v>
       </c>
       <c r="J49" s="3">
-        <v>481000</v>
+        <v>383000</v>
       </c>
       <c r="K49" s="3">
         <v>481000</v>
       </c>
       <c r="L49" s="3">
+        <v>481000</v>
+      </c>
+      <c r="M49" s="3">
         <v>628000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>481000</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>11</v>
@@ -2927,14 +3038,17 @@
       <c r="S49" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2992,8 +3106,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3051,67 +3168,73 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1474000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1442000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1384000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1214000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1399000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1348000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1043000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1083000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>870000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1761000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1502000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1154000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1436000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1377000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1071000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1089000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>486000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>468000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>212000</v>
       </c>
     </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3169,67 +3292,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>29756000</v>
+      </c>
+      <c r="E54" s="3">
         <v>28479000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>28856000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>29558000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>30009000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>18505000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17656000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17455000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16509000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17227000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16811000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>13411000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>13706000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14672000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15262000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>15023000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>15949000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>23513000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>22345000</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3251,8 +3380,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3274,362 +3404,381 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1080000</v>
+      </c>
+      <c r="E57" s="3">
         <v>807000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1145000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>957000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1215000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>825000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>558000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>549000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>719000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>556000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>661000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>455000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>495000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>474000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>520000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>483000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>618000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>952000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1382000</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>835000</v>
+      </c>
+      <c r="E58" s="3">
         <v>877000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>938000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1067000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1085000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>373000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>354000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>336000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>310000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>435000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>967000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>803000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>207000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>415000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>420000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>190000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>152000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>400000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1033000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1228000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1389000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1827000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>711000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>510000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>623000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>241000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>290000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>233000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>226000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>485000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>249000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>370000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>616000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>202000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>156000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>226000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>237000</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2948000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2912000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3472000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3851000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3011000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1708000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1535000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1126000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1319000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1224000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1854000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1743000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>951000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1259000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1556000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>875000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>926000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1578000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1946000</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5324000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4856000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4581000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6012000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6964000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5264000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4645000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4722000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4111000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4175000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3952000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3026000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3756000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4588000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4842000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5491000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5555000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8953000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8106000</v>
       </c>
     </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6209000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5906000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5960000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5380000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6424000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4230000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4249000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4309000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3403000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4296000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3726000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1644000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1848000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1908000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1784000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2288000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2047000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3269000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2880000</v>
       </c>
     </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3687,8 +3836,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3746,8 +3898,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3805,67 +3960,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14481000</v>
+      </c>
+      <c r="E66" s="3">
         <v>13674000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14013000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>15243000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16399000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11202000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10429000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10157000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8833000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9695000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9532000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6413000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6555000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7755000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8182000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8654000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8528000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13800000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>12928000</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3887,8 +4048,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3946,8 +4108,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4005,8 +4170,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4064,8 +4232,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4123,67 +4294,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>887000</v>
+      </c>
+      <c r="E72" s="3">
         <v>418000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>142000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-559000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-419000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-623000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-865000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-758000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-359000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-514000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-774000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1230000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1339000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1487000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-980000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1045000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>122000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2070000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2166000</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4241,8 +4418,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4300,8 +4480,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4359,67 +4542,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15275000</v>
+      </c>
+      <c r="E76" s="3">
         <v>14805000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14843000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14315000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13610000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7303000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7227000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7298000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7676000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7532000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7279000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6998000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7151000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6917000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7080000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6369000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7421000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9713000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9417000</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4477,131 +4666,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44196</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44012</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43830</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43646</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43465</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43281</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43100</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>42916</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>42735</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>42551</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>42369</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>42185</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>626000</v>
+      </c>
+      <c r="E81" s="3">
         <v>790000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>945000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1167000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>304000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>354000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-68000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-289000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>286000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>388000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>526000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>104000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>146000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-506000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>57000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1104000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1983000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>30000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4623,8 +4821,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4682,8 +4881,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4741,8 +4943,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4800,8 +5005,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4859,8 +5067,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4918,8 +5129,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4977,67 +5191,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1746000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1554000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2343000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2137000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1330000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>942000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>638000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>838000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>995000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1051000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>934000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>644000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>586000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>662000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>566000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>291000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>562000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>532000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1099000</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5059,67 +5279,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1282000</v>
+        <v>-1296000</v>
       </c>
       <c r="E91" s="3">
+        <v>-1073000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-929000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-778000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-611000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-492000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-365000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1100000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-490000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>3000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2211000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1694000</v>
       </c>
     </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5177,8 +5401,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5236,67 +5463,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1495000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1401000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1057000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-612000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>197000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-334000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-342000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1119000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-674000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-359000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2115000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-258000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-312000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-222000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-225000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>20000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-600000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-992000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1799000</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5318,41 +5551,42 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-279000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-498000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-248000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-288000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-117000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-104000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-44000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-92000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-124000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-127000</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -5366,19 +5600,22 @@
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-43000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-78000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-83000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-115000</v>
       </c>
     </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5436,8 +5673,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5495,8 +5735,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5554,181 +5797,193 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-122000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-738000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2272000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1129000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-960000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>479000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-255000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>501000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-460000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-791000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1010000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-120000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1298000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-220000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>664000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-121000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1033000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>333000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1016000</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-12000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-22000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-8000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>11000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>16000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-25000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-9000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2000</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-5000</v>
       </c>
       <c r="N101" s="3">
         <v>-5000</v>
       </c>
       <c r="O101" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="P101" s="3">
         <v>7000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>5000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>23000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-590000</v>
+        <v>229000</v>
       </c>
       <c r="E102" s="3">
+        <v>-664000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-998000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>374000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>559000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1098000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>57000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>195000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-148000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-101000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-176000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>261000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-995000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>200000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>992000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>195000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>707000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-328000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>327000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SSLZY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSLZY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
   <si>
     <t>SSLZY</t>
   </si>
@@ -656,293 +656,306 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44561</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44377</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44196</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44012</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43830</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43646</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43465</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43281</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>42916</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>42735</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>42551</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>42369</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>42185</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2780000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2977000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3057000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4144000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3843000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2725000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2112000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1784000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1728000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2143000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2043000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2046000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1727000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1692000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1506000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1403000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1191000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1181000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1261000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2150000</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1699000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1830000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1837000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1990000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1912000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1499000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1485000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1398000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1245000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1457000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1241000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1149000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1162000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1253000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1066000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1069000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1055000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1001000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>882000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1570000</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1081000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1147000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1220000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2154000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1931000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1226000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>627000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>386000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>483000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>686000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>802000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>897000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>565000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>439000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>440000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>334000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>136000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>180000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>379000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>580000</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -965,70 +978,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E12" s="3">
         <v>37000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>49000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>45000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>103000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>85000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>41000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>34000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>25000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>75000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>28000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>60000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>45000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>41000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>53000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>91000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>47000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>36000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>152000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>154000</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1089,70 +1106,76 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E14" s="3">
         <v>54000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>24000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>320000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>39000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>68000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>8000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>134000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>755000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>52000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>25000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>100000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>76000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-34000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>951000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>44000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1477000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2854000</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>2289000</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1174,20 +1197,20 @@
       <c r="I15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K15" s="3">
         <v>1000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="s">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3000</v>
-      </c>
-      <c r="N15" s="3">
-        <v>1000</v>
       </c>
       <c r="O15" s="3">
         <v>1000</v>
@@ -1202,19 +1225,22 @@
         <v>1000</v>
       </c>
       <c r="S15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T15" s="3">
         <v>4000</v>
-      </c>
-      <c r="T15" s="3">
-        <v>1000</v>
       </c>
       <c r="U15" s="3">
         <v>1000</v>
       </c>
-      <c r="V15" s="3" t="s">
+      <c r="V15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W15" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1234,132 +1260,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1901000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2134000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2081000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2826000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2213000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1999000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1633000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1699000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2119000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1715000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1453000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1275000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1392000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1535000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2248000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1286000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2793000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3953000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1087000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3834000</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>879000</v>
+      </c>
+      <c r="E18" s="3">
         <v>843000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>976000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1318000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1630000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>726000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>479000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>85000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-391000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>428000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>590000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>771000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>335000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>157000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-742000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>117000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1602000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2772000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>174000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1684000</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1382,8 +1415,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1444,70 +1478,76 @@
       <c r="V20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1724000</v>
+      </c>
+      <c r="E21" s="3">
         <v>799000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1927000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1359000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2483000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>741000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1093000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>128000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>95000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>510000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1050000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>782000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>663000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>203000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-394000</v>
       </c>
-      <c r="R21" s="3" t="s">
+      <c r="S21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1203000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2731000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>550000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1554000</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1568,132 +1608,141 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>879000</v>
+      </c>
+      <c r="E23" s="3">
         <v>843000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>976000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1318000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1630000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>726000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>479000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>85000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-391000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>428000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>590000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>771000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>335000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>157000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-742000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>117000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1602000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2772000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>174000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1684000</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>220000</v>
+      </c>
+      <c r="E24" s="3">
         <v>217000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>186000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>373000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>463000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>422000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>125000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>153000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-102000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>142000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>202000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>245000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>231000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>11000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-236000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>60000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-498000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-789000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>144000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-543000</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1754,132 +1803,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>659000</v>
+      </c>
+      <c r="E26" s="3">
         <v>626000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>790000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>945000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1167000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>304000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>354000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-68000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-289000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>286000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>388000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>526000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>104000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>146000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-506000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>57000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1104000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1983000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>30000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>636000</v>
+      </c>
+      <c r="E27" s="3">
         <v>626000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>790000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>945000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1167000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>304000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>354000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-68000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-289000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>286000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>388000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>526000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>104000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>146000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-506000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>57000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1104000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1983000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>30000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1940,8 +1998,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2002,8 +2063,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2064,8 +2128,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2126,8 +2193,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2188,70 +2258,76 @@
       <c r="V32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>636000</v>
+      </c>
+      <c r="E33" s="3">
         <v>626000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>790000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>945000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1167000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>304000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>354000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-68000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-289000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>286000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>388000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>526000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>104000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>146000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-506000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>57000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1104000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1983000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>30000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2312,137 +2388,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>636000</v>
+      </c>
+      <c r="E35" s="3">
         <v>626000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>790000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>945000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1167000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>304000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>354000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-68000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-289000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>286000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>388000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>526000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>104000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>146000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-506000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>57000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1104000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1983000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>30000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44561</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44377</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44196</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44012</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43830</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43646</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43465</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43281</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>42916</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>42735</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>42551</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>42369</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>42185</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2465,8 +2550,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2489,542 +2575,567 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1659000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1875000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1840000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2352000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3279000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2976000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2417000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1319000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1262000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1067000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1215000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1316000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1492000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1231000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2226000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2026000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1034000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1343000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>399000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>775000</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E42" s="3">
         <v>404000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>91000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>109000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>85000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>29000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>25000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>195000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>14000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>28000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>14000</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>17000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>7000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>651000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>66000</v>
       </c>
     </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>892000</v>
+      </c>
+      <c r="E43" s="3">
         <v>915000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>810000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>843000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>851000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>995000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>703000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>583000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>540000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>577000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>423000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>562000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>451000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>447000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>370000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>382000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>532000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>477000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>650000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>690000</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>418000</v>
+      </c>
+      <c r="E44" s="3">
         <v>442000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>455000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>443000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>470000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>406000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>294000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>288000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>284000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>301000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>304000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>288000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>252000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>266000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>284000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>321000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>379000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>360000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>526000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>443000</v>
       </c>
     </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E45" s="3">
         <v>711000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1331000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1381000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1333000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>367000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>281000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>477000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>25000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>40000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>32000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>293000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>28000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>32000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>214000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>45000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>448000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>86000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>91000</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3103000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4347000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4527000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5128000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6018000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4751000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3696000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2696000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2136000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2180000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1966000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2226000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2502000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1972000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2929000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2950000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1991000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2125000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1662000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2065000</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>712000</v>
+        <v>550000</v>
       </c>
       <c r="E47" s="3">
-        <v>693000</v>
+        <v>585000</v>
       </c>
       <c r="F47" s="3">
-        <v>660000</v>
+        <v>612000</v>
       </c>
       <c r="G47" s="3">
-        <v>693000</v>
+        <v>631000</v>
       </c>
       <c r="H47" s="3">
-        <v>749000</v>
+        <v>634000</v>
       </c>
       <c r="I47" s="3">
-        <v>510000</v>
+        <v>696000</v>
       </c>
       <c r="J47" s="3">
+        <v>493000</v>
+      </c>
+      <c r="K47" s="3">
         <v>543000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>959000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>172000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>157000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>219000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>82000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>177000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>197000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>213000</v>
-      </c>
-      <c r="S47" s="3">
-        <v>233000</v>
       </c>
       <c r="T47" s="3">
         <v>233000</v>
       </c>
       <c r="U47" s="3">
+        <v>233000</v>
+      </c>
+      <c r="V47" s="3">
         <v>287000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>273000</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22978000</v>
+      </c>
+      <c r="E48" s="3">
         <v>21972000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20627000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20494000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20297000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21647000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>12568000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12991000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12796000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12806000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12715000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12383000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9673000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10121000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10169000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11028000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11710000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13105000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>21096000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>19795000</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1319000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1251000</v>
-      </c>
-      <c r="E49" s="3">
-        <v>1190000</v>
       </c>
       <c r="F49" s="3">
         <v>1190000</v>
       </c>
       <c r="G49" s="3">
+        <v>1190000</v>
+      </c>
+      <c r="H49" s="3">
         <v>1336000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1463000</v>
-      </c>
-      <c r="I49" s="3">
-        <v>383000</v>
       </c>
       <c r="J49" s="3">
         <v>383000</v>
       </c>
       <c r="K49" s="3">
-        <v>481000</v>
+        <v>383000</v>
       </c>
       <c r="L49" s="3">
         <v>481000</v>
       </c>
       <c r="M49" s="3">
+        <v>481000</v>
+      </c>
+      <c r="N49" s="3">
         <v>628000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>481000</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>11</v>
@@ -3041,14 +3152,17 @@
       <c r="T49" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3109,8 +3223,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3171,70 +3288,76 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1474000</v>
+        <v>1600000</v>
       </c>
       <c r="E52" s="3">
-        <v>1442000</v>
+        <v>1601000</v>
       </c>
       <c r="F52" s="3">
-        <v>1384000</v>
+        <v>1523000</v>
       </c>
       <c r="G52" s="3">
-        <v>1214000</v>
+        <v>1413000</v>
       </c>
       <c r="H52" s="3">
-        <v>1399000</v>
+        <v>1273000</v>
       </c>
       <c r="I52" s="3">
-        <v>1348000</v>
+        <v>1452000</v>
       </c>
       <c r="J52" s="3">
+        <v>1365000</v>
+      </c>
+      <c r="K52" s="3">
         <v>1043000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1083000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>870000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1761000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1502000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1154000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1436000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1377000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1071000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1089000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>486000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>468000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>212000</v>
       </c>
     </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3295,70 +3418,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>29550000</v>
+      </c>
+      <c r="E54" s="3">
         <v>29756000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>28479000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>28856000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>29558000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>30009000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>18505000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17656000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17455000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16509000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>17227000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16811000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>13411000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>13706000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14672000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>15262000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>15023000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>15949000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>23513000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>22345000</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3381,8 +3510,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3405,380 +3535,399 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>973000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1080000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>807000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1145000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>957000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1215000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>825000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>558000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>549000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>719000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>556000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>661000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>455000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>495000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>474000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>520000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>483000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>618000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>952000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1382000</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>981000</v>
+      </c>
+      <c r="E58" s="3">
         <v>835000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>877000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>938000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1067000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1085000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>373000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>354000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>336000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>310000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>435000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>967000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>803000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>207000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>415000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>420000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>190000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>152000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>400000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>830000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1033000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1228000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1389000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1827000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>711000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>510000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>623000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>241000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>290000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>233000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>226000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>485000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>249000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>370000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>616000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>202000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>156000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>226000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>237000</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2784000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2948000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2912000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3472000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3851000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3011000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1708000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1535000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1126000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1319000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1224000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1854000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1743000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>951000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1259000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1556000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>875000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>926000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1578000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1946000</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5494000</v>
+      </c>
+      <c r="E61" s="3">
         <v>5324000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4856000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4581000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6012000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6964000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5264000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4645000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4722000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4111000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4175000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3952000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3026000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3756000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4588000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4842000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5491000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5555000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8953000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8106000</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5629000</v>
+      </c>
+      <c r="E62" s="3">
         <v>6209000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5906000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5960000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5380000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6424000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4230000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4249000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4309000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3403000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4296000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3726000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1644000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1848000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1908000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1784000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2288000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2047000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3269000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2880000</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3839,8 +3988,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3901,8 +4053,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3963,70 +4118,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14106000</v>
+      </c>
+      <c r="E66" s="3">
         <v>14481000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>13674000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14013000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15243000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16399000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11202000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10429000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10157000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8833000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9695000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9532000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6413000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6555000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7755000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8182000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8654000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8528000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13800000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>12928000</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4049,8 +4210,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4111,8 +4273,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4173,8 +4338,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4235,8 +4403,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4297,70 +4468,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1102000</v>
+      </c>
+      <c r="E72" s="3">
         <v>887000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>418000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>142000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-559000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-419000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-623000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-865000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-758000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-359000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-514000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-774000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1230000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1339000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1487000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-980000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1045000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>122000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2070000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2166000</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4421,8 +4598,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4483,8 +4663,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4545,70 +4728,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15444000</v>
+      </c>
+      <c r="E76" s="3">
         <v>15275000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14805000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14843000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14315000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13610000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7303000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7227000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7298000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7676000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7532000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7279000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6998000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7151000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6917000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7080000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6369000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7421000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9713000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9417000</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4669,137 +4858,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44561</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44377</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44196</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44012</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43830</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43646</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43465</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43281</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>42916</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>42735</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>42551</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>42369</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>42185</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>636000</v>
+      </c>
+      <c r="E81" s="3">
         <v>626000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>790000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>945000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1167000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>304000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>354000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-68000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-289000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>286000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>388000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>526000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>104000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>146000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-506000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>57000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1104000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1983000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>30000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4822,8 +5020,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4884,8 +5083,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4946,8 +5148,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5008,8 +5213,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5070,8 +5278,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5132,8 +5343,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5194,70 +5408,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1476000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1746000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1554000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2343000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2137000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1330000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>942000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>638000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>838000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>995000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1051000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>934000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>644000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>586000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>662000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>566000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>291000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>562000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>532000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1099000</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5280,70 +5500,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1173000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1296000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1073000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-929000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-778000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-611000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-492000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-365000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1100000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-490000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>3000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2211000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1694000</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5404,8 +5628,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5466,70 +5693,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1396000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1495000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1401000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1057000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-612000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>197000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-334000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-342000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1119000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-674000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-359000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2115000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-258000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-312000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-222000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-225000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>20000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-600000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-992000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1799000</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5552,44 +5785,45 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-568000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-279000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-498000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-248000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-288000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-117000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-104000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-44000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-92000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-124000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-127000</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -5603,19 +5837,22 @@
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-43000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-78000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-83000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-115000</v>
       </c>
     </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5676,8 +5913,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5738,8 +5978,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5800,190 +6043,202 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-285000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-122000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-738000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2272000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1129000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-960000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>479000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-255000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>501000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-460000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-791000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1010000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-120000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1298000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-220000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>664000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-121000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1033000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>333000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1016000</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-16000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-5000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-12000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-22000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-8000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>11000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>16000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-25000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-9000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2000</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-5000</v>
       </c>
       <c r="O101" s="3">
         <v>-5000</v>
       </c>
       <c r="P101" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="Q101" s="3">
         <v>7000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>5000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>23000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-216000</v>
+      </c>
+      <c r="E102" s="3">
         <v>229000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-664000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-998000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>374000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>559000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1098000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>57000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>195000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-148000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-101000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-176000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>261000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-995000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>200000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>992000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>195000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>707000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-328000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>327000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SSLZY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSLZY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="92">
   <si>
     <t>SSLZY</t>
   </si>
@@ -663,13 +663,11 @@
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -703,22 +701,22 @@
         <v>45473</v>
       </c>
       <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44377</v>
       </c>
       <c r="K7" s="2">
         <v>44196</v>
@@ -764,26 +762,26 @@
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>2780000</v>
-      </c>
-      <c r="E8" s="3">
-        <v>2977000</v>
-      </c>
-      <c r="F8" s="3">
-        <v>3057000</v>
-      </c>
-      <c r="G8" s="3">
-        <v>4144000</v>
-      </c>
-      <c r="H8" s="3">
-        <v>3843000</v>
-      </c>
-      <c r="I8" s="3">
-        <v>2725000</v>
-      </c>
-      <c r="J8" s="3">
-        <v>2112000</v>
+      <c r="D8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K8" s="3">
         <v>1784000</v>
@@ -829,26 +827,26 @@
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>1699000</v>
-      </c>
-      <c r="E9" s="3">
-        <v>1830000</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1837000</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1990000</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1912000</v>
-      </c>
-      <c r="I9" s="3">
-        <v>1499000</v>
-      </c>
-      <c r="J9" s="3">
-        <v>1485000</v>
+      <c r="D9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K9" s="3">
         <v>1398000</v>
@@ -894,26 +892,26 @@
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>1081000</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1147000</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1220000</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2154000</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1931000</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1226000</v>
-      </c>
-      <c r="J10" s="3">
-        <v>627000</v>
+      <c r="D10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K10" s="3">
         <v>386000</v>
@@ -984,26 +982,26 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>33000</v>
-      </c>
-      <c r="E12" s="3">
-        <v>37000</v>
-      </c>
-      <c r="F12" s="3">
-        <v>49000</v>
-      </c>
-      <c r="G12" s="3">
-        <v>45000</v>
-      </c>
-      <c r="H12" s="3">
-        <v>103000</v>
-      </c>
-      <c r="I12" s="3">
-        <v>85000</v>
-      </c>
-      <c r="J12" s="3">
-        <v>41000</v>
+      <c r="D12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K12" s="3">
         <v>34000</v>
@@ -1114,26 +1112,26 @@
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>25000</v>
-      </c>
-      <c r="E14" s="3">
-        <v>54000</v>
-      </c>
-      <c r="F14" s="3">
-        <v>24000</v>
-      </c>
-      <c r="G14" s="3">
-        <v>320000</v>
-      </c>
-      <c r="H14" s="3">
-        <v>39000</v>
-      </c>
-      <c r="I14" s="3">
-        <v>68000</v>
-      </c>
-      <c r="J14" s="3">
-        <v>8000</v>
+      <c r="D14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K14" s="3">
         <v>134000</v>
@@ -1266,26 +1264,26 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>1901000</v>
-      </c>
-      <c r="E17" s="3">
-        <v>2134000</v>
-      </c>
-      <c r="F17" s="3">
-        <v>2081000</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2826000</v>
-      </c>
-      <c r="H17" s="3">
-        <v>2213000</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1999000</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1633000</v>
+      <c r="D17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K17" s="3">
         <v>1699000</v>
@@ -1331,26 +1329,26 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>879000</v>
-      </c>
-      <c r="E18" s="3">
-        <v>843000</v>
-      </c>
-      <c r="F18" s="3">
-        <v>976000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1318000</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1630000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>726000</v>
-      </c>
-      <c r="J18" s="3">
-        <v>479000</v>
+      <c r="D18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K18" s="3">
         <v>85000</v>
@@ -1421,26 +1419,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1486,26 +1484,26 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>1724000</v>
-      </c>
-      <c r="E21" s="3">
-        <v>799000</v>
-      </c>
-      <c r="F21" s="3">
-        <v>1927000</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1359000</v>
-      </c>
-      <c r="H21" s="3">
-        <v>2483000</v>
-      </c>
-      <c r="I21" s="3">
-        <v>741000</v>
-      </c>
-      <c r="J21" s="3">
-        <v>1093000</v>
+      <c r="D21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K21" s="3">
         <v>128000</v>
@@ -1551,26 +1549,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1616,26 +1614,26 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>879000</v>
-      </c>
-      <c r="E23" s="3">
-        <v>843000</v>
-      </c>
-      <c r="F23" s="3">
-        <v>976000</v>
-      </c>
-      <c r="G23" s="3">
-        <v>1318000</v>
-      </c>
-      <c r="H23" s="3">
-        <v>1630000</v>
-      </c>
-      <c r="I23" s="3">
-        <v>726000</v>
-      </c>
-      <c r="J23" s="3">
-        <v>479000</v>
+      <c r="D23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K23" s="3">
         <v>85000</v>
@@ -1681,26 +1679,26 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>220000</v>
-      </c>
-      <c r="E24" s="3">
-        <v>217000</v>
-      </c>
-      <c r="F24" s="3">
-        <v>186000</v>
-      </c>
-      <c r="G24" s="3">
-        <v>373000</v>
-      </c>
-      <c r="H24" s="3">
-        <v>463000</v>
-      </c>
-      <c r="I24" s="3">
-        <v>422000</v>
-      </c>
-      <c r="J24" s="3">
-        <v>125000</v>
+      <c r="D24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K24" s="3">
         <v>153000</v>
@@ -1811,26 +1809,26 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>659000</v>
-      </c>
-      <c r="E26" s="3">
-        <v>626000</v>
-      </c>
-      <c r="F26" s="3">
-        <v>790000</v>
-      </c>
-      <c r="G26" s="3">
-        <v>945000</v>
-      </c>
-      <c r="H26" s="3">
-        <v>1167000</v>
-      </c>
-      <c r="I26" s="3">
-        <v>304000</v>
-      </c>
-      <c r="J26" s="3">
-        <v>354000</v>
+      <c r="D26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K26" s="3">
         <v>-68000</v>
@@ -1876,26 +1874,26 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>636000</v>
-      </c>
-      <c r="E27" s="3">
-        <v>626000</v>
-      </c>
-      <c r="F27" s="3">
-        <v>790000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>945000</v>
-      </c>
-      <c r="H27" s="3">
-        <v>1167000</v>
-      </c>
-      <c r="I27" s="3">
-        <v>304000</v>
-      </c>
-      <c r="J27" s="3">
-        <v>354000</v>
+      <c r="D27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K27" s="3">
         <v>-68000</v>
@@ -2006,26 +2004,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -2201,26 +2199,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2266,26 +2264,26 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>636000</v>
-      </c>
-      <c r="E33" s="3">
-        <v>626000</v>
-      </c>
-      <c r="F33" s="3">
-        <v>790000</v>
-      </c>
-      <c r="G33" s="3">
-        <v>945000</v>
-      </c>
-      <c r="H33" s="3">
-        <v>1167000</v>
-      </c>
-      <c r="I33" s="3">
-        <v>304000</v>
-      </c>
-      <c r="J33" s="3">
-        <v>354000</v>
+      <c r="D33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K33" s="3">
         <v>-68000</v>
@@ -2396,26 +2394,26 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>636000</v>
-      </c>
-      <c r="E35" s="3">
-        <v>626000</v>
-      </c>
-      <c r="F35" s="3">
-        <v>790000</v>
-      </c>
-      <c r="G35" s="3">
-        <v>945000</v>
-      </c>
-      <c r="H35" s="3">
-        <v>1167000</v>
-      </c>
-      <c r="I35" s="3">
-        <v>304000</v>
-      </c>
-      <c r="J35" s="3">
-        <v>354000</v>
+      <c r="D35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K35" s="3">
         <v>-68000</v>
@@ -2470,22 +2468,22 @@
         <v>45473</v>
       </c>
       <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44377</v>
       </c>
       <c r="K38" s="2">
         <v>44196</v>
@@ -2585,22 +2583,22 @@
         <v>1659000</v>
       </c>
       <c r="E41" s="3">
+        <v>1659000</v>
+      </c>
+      <c r="F41" s="3">
         <v>1875000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
+        <v>1875000</v>
+      </c>
+      <c r="H41" s="3">
         <v>1840000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
+        <v>1840000</v>
+      </c>
+      <c r="J41" s="3">
         <v>2352000</v>
-      </c>
-      <c r="H41" s="3">
-        <v>3279000</v>
-      </c>
-      <c r="I41" s="3">
-        <v>2976000</v>
-      </c>
-      <c r="J41" s="3">
-        <v>2417000</v>
       </c>
       <c r="K41" s="3">
         <v>1319000</v>
@@ -2647,25 +2645,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>404000</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>91000</v>
+        <v>252000</v>
       </c>
       <c r="G42" s="3">
-        <v>109000</v>
+        <v>252000</v>
       </c>
       <c r="H42" s="3">
-        <v>85000</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>1000</v>
+        <v>55000</v>
       </c>
       <c r="K42" s="3">
         <v>29000</v>
@@ -2715,22 +2713,22 @@
         <v>892000</v>
       </c>
       <c r="E43" s="3">
-        <v>915000</v>
+        <v>892000</v>
       </c>
       <c r="F43" s="3">
+        <v>932000</v>
+      </c>
+      <c r="G43" s="3">
+        <v>932000</v>
+      </c>
+      <c r="H43" s="3">
         <v>810000</v>
       </c>
-      <c r="G43" s="3">
-        <v>843000</v>
-      </c>
-      <c r="H43" s="3">
-        <v>851000</v>
-      </c>
       <c r="I43" s="3">
-        <v>995000</v>
+        <v>810000</v>
       </c>
       <c r="J43" s="3">
-        <v>703000</v>
+        <v>879000</v>
       </c>
       <c r="K43" s="3">
         <v>583000</v>
@@ -2780,22 +2778,22 @@
         <v>418000</v>
       </c>
       <c r="E44" s="3">
+        <v>418000</v>
+      </c>
+      <c r="F44" s="3">
         <v>442000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
+        <v>442000</v>
+      </c>
+      <c r="H44" s="3">
         <v>455000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
+        <v>455000</v>
+      </c>
+      <c r="J44" s="3">
         <v>443000</v>
-      </c>
-      <c r="H44" s="3">
-        <v>470000</v>
-      </c>
-      <c r="I44" s="3">
-        <v>406000</v>
-      </c>
-      <c r="J44" s="3">
-        <v>294000</v>
       </c>
       <c r="K44" s="3">
         <v>288000</v>
@@ -2842,25 +2840,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>54000</v>
+        <v>80000</v>
       </c>
       <c r="E45" s="3">
-        <v>711000</v>
+        <v>80000</v>
       </c>
       <c r="F45" s="3">
-        <v>1331000</v>
+        <v>752000</v>
       </c>
       <c r="G45" s="3">
-        <v>1381000</v>
+        <v>752000</v>
       </c>
       <c r="H45" s="3">
-        <v>1333000</v>
+        <v>1392000</v>
       </c>
       <c r="I45" s="3">
-        <v>367000</v>
+        <v>1392000</v>
       </c>
       <c r="J45" s="3">
-        <v>281000</v>
+        <v>1329000</v>
       </c>
       <c r="K45" s="3">
         <v>477000</v>
@@ -2910,22 +2908,22 @@
         <v>3103000</v>
       </c>
       <c r="E46" s="3">
+        <v>3103000</v>
+      </c>
+      <c r="F46" s="3">
         <v>4347000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
+        <v>4347000</v>
+      </c>
+      <c r="H46" s="3">
         <v>4527000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
+        <v>4527000</v>
+      </c>
+      <c r="J46" s="3">
         <v>5128000</v>
-      </c>
-      <c r="H46" s="3">
-        <v>6018000</v>
-      </c>
-      <c r="I46" s="3">
-        <v>4751000</v>
-      </c>
-      <c r="J46" s="3">
-        <v>3696000</v>
       </c>
       <c r="K46" s="3">
         <v>2696000</v>
@@ -2972,25 +2970,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>550000</v>
+        <v>415000</v>
       </c>
       <c r="E47" s="3">
-        <v>585000</v>
+        <v>415000</v>
       </c>
       <c r="F47" s="3">
-        <v>612000</v>
+        <v>406000</v>
       </c>
       <c r="G47" s="3">
-        <v>631000</v>
+        <v>406000</v>
       </c>
       <c r="H47" s="3">
-        <v>634000</v>
+        <v>400000</v>
       </c>
       <c r="I47" s="3">
-        <v>696000</v>
+        <v>400000</v>
       </c>
       <c r="J47" s="3">
-        <v>493000</v>
+        <v>379000</v>
       </c>
       <c r="K47" s="3">
         <v>543000</v>
@@ -3040,22 +3038,22 @@
         <v>22978000</v>
       </c>
       <c r="E48" s="3">
+        <v>22978000</v>
+      </c>
+      <c r="F48" s="3">
         <v>21972000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
+        <v>21972000</v>
+      </c>
+      <c r="H48" s="3">
         <v>20627000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
+        <v>20627000</v>
+      </c>
+      <c r="J48" s="3">
         <v>20494000</v>
-      </c>
-      <c r="H48" s="3">
-        <v>20297000</v>
-      </c>
-      <c r="I48" s="3">
-        <v>21647000</v>
-      </c>
-      <c r="J48" s="3">
-        <v>12568000</v>
       </c>
       <c r="K48" s="3">
         <v>12991000</v>
@@ -3105,22 +3103,22 @@
         <v>1319000</v>
       </c>
       <c r="E49" s="3">
+        <v>1319000</v>
+      </c>
+      <c r="F49" s="3">
         <v>1251000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
+        <v>1251000</v>
+      </c>
+      <c r="H49" s="3">
         <v>1190000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1190000</v>
       </c>
-      <c r="H49" s="3">
-        <v>1336000</v>
-      </c>
-      <c r="I49" s="3">
-        <v>1463000</v>
-      </c>
       <c r="J49" s="3">
-        <v>383000</v>
+        <v>1190000</v>
       </c>
       <c r="K49" s="3">
         <v>383000</v>
@@ -3297,25 +3295,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1600000</v>
+        <v>637000</v>
       </c>
       <c r="E52" s="3">
-        <v>1601000</v>
+        <v>637000</v>
       </c>
       <c r="F52" s="3">
-        <v>1523000</v>
+        <v>502000</v>
       </c>
       <c r="G52" s="3">
-        <v>1413000</v>
+        <v>502000</v>
       </c>
       <c r="H52" s="3">
-        <v>1273000</v>
+        <v>423000</v>
       </c>
       <c r="I52" s="3">
-        <v>1452000</v>
+        <v>423000</v>
       </c>
       <c r="J52" s="3">
-        <v>1365000</v>
+        <v>299000</v>
       </c>
       <c r="K52" s="3">
         <v>1043000</v>
@@ -3430,22 +3428,22 @@
         <v>29550000</v>
       </c>
       <c r="E54" s="3">
+        <v>29550000</v>
+      </c>
+      <c r="F54" s="3">
         <v>29756000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
+        <v>29756000</v>
+      </c>
+      <c r="H54" s="3">
         <v>28479000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
+        <v>28479000</v>
+      </c>
+      <c r="J54" s="3">
         <v>28856000</v>
-      </c>
-      <c r="H54" s="3">
-        <v>29558000</v>
-      </c>
-      <c r="I54" s="3">
-        <v>30009000</v>
-      </c>
-      <c r="J54" s="3">
-        <v>18505000</v>
       </c>
       <c r="K54" s="3">
         <v>17656000</v>
@@ -3545,22 +3543,22 @@
         <v>973000</v>
       </c>
       <c r="E57" s="3">
-        <v>1080000</v>
+        <v>973000</v>
       </c>
       <c r="F57" s="3">
+        <v>567000</v>
+      </c>
+      <c r="G57" s="3">
+        <v>567000</v>
+      </c>
+      <c r="H57" s="3">
         <v>807000</v>
       </c>
-      <c r="G57" s="3">
-        <v>1145000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>957000</v>
-      </c>
       <c r="I57" s="3">
-        <v>1215000</v>
+        <v>807000</v>
       </c>
       <c r="J57" s="3">
-        <v>825000</v>
+        <v>805000</v>
       </c>
       <c r="K57" s="3">
         <v>558000</v>
@@ -3610,22 +3608,22 @@
         <v>981000</v>
       </c>
       <c r="E58" s="3">
+        <v>981000</v>
+      </c>
+      <c r="F58" s="3">
         <v>835000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
+        <v>835000</v>
+      </c>
+      <c r="H58" s="3">
         <v>877000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
+        <v>877000</v>
+      </c>
+      <c r="J58" s="3">
         <v>938000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1067000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1085000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>373000</v>
       </c>
       <c r="K58" s="3">
         <v>354000</v>
@@ -3675,22 +3673,22 @@
         <v>830000</v>
       </c>
       <c r="E59" s="3">
-        <v>1033000</v>
+        <v>830000</v>
       </c>
       <c r="F59" s="3">
+        <v>1441000</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1441000</v>
+      </c>
+      <c r="H59" s="3">
         <v>1228000</v>
       </c>
-      <c r="G59" s="3">
-        <v>1389000</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1827000</v>
-      </c>
       <c r="I59" s="3">
-        <v>711000</v>
+        <v>1228000</v>
       </c>
       <c r="J59" s="3">
-        <v>510000</v>
+        <v>1613000</v>
       </c>
       <c r="K59" s="3">
         <v>623000</v>
@@ -3740,22 +3738,22 @@
         <v>2784000</v>
       </c>
       <c r="E60" s="3">
+        <v>2784000</v>
+      </c>
+      <c r="F60" s="3">
         <v>2948000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
+        <v>2948000</v>
+      </c>
+      <c r="H60" s="3">
         <v>2912000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
+        <v>2912000</v>
+      </c>
+      <c r="J60" s="3">
         <v>3472000</v>
-      </c>
-      <c r="H60" s="3">
-        <v>3851000</v>
-      </c>
-      <c r="I60" s="3">
-        <v>3011000</v>
-      </c>
-      <c r="J60" s="3">
-        <v>1708000</v>
       </c>
       <c r="K60" s="3">
         <v>1535000</v>
@@ -3805,22 +3803,22 @@
         <v>5494000</v>
       </c>
       <c r="E61" s="3">
+        <v>5494000</v>
+      </c>
+      <c r="F61" s="3">
         <v>5324000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
+        <v>5324000</v>
+      </c>
+      <c r="H61" s="3">
         <v>4856000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
+        <v>4856000</v>
+      </c>
+      <c r="J61" s="3">
         <v>4581000</v>
-      </c>
-      <c r="H61" s="3">
-        <v>6012000</v>
-      </c>
-      <c r="I61" s="3">
-        <v>6964000</v>
-      </c>
-      <c r="J61" s="3">
-        <v>5264000</v>
       </c>
       <c r="K61" s="3">
         <v>4645000</v>
@@ -3867,25 +3865,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5629000</v>
+        <v>3646000</v>
       </c>
       <c r="E62" s="3">
-        <v>6209000</v>
+        <v>3646000</v>
       </c>
       <c r="F62" s="3">
-        <v>5906000</v>
+        <v>4152000</v>
       </c>
       <c r="G62" s="3">
-        <v>5960000</v>
+        <v>4152000</v>
       </c>
       <c r="H62" s="3">
-        <v>5380000</v>
+        <v>3875000</v>
       </c>
       <c r="I62" s="3">
-        <v>6424000</v>
+        <v>3875000</v>
       </c>
       <c r="J62" s="3">
-        <v>4230000</v>
+        <v>3822000</v>
       </c>
       <c r="K62" s="3">
         <v>4249000</v>
@@ -4127,25 +4125,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>14106000</v>
+        <v>13907000</v>
       </c>
       <c r="E66" s="3">
+        <v>13907000</v>
+      </c>
+      <c r="F66" s="3">
         <v>14481000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
+        <v>14481000</v>
+      </c>
+      <c r="H66" s="3">
         <v>13674000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
+        <v>13674000</v>
+      </c>
+      <c r="J66" s="3">
         <v>14013000</v>
-      </c>
-      <c r="H66" s="3">
-        <v>15243000</v>
-      </c>
-      <c r="I66" s="3">
-        <v>16399000</v>
-      </c>
-      <c r="J66" s="3">
-        <v>11202000</v>
       </c>
       <c r="K66" s="3">
         <v>10429000</v>
@@ -4477,25 +4475,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1102000</v>
+        <v>2064000</v>
       </c>
       <c r="E72" s="3">
-        <v>887000</v>
+        <v>2064000</v>
       </c>
       <c r="F72" s="3">
-        <v>418000</v>
+        <v>1792000</v>
       </c>
       <c r="G72" s="3">
-        <v>142000</v>
+        <v>1792000</v>
       </c>
       <c r="H72" s="3">
-        <v>-559000</v>
+        <v>1437000</v>
       </c>
       <c r="I72" s="3">
-        <v>-419000</v>
+        <v>1437000</v>
       </c>
       <c r="J72" s="3">
-        <v>-623000</v>
+        <v>1153000</v>
       </c>
       <c r="K72" s="3">
         <v>-865000</v>
@@ -4740,22 +4738,22 @@
         <v>15444000</v>
       </c>
       <c r="E76" s="3">
+        <v>15444000</v>
+      </c>
+      <c r="F76" s="3">
         <v>15275000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
+        <v>15275000</v>
+      </c>
+      <c r="H76" s="3">
         <v>14805000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
+        <v>14805000</v>
+      </c>
+      <c r="J76" s="3">
         <v>14843000</v>
-      </c>
-      <c r="H76" s="3">
-        <v>14315000</v>
-      </c>
-      <c r="I76" s="3">
-        <v>13610000</v>
-      </c>
-      <c r="J76" s="3">
-        <v>7303000</v>
       </c>
       <c r="K76" s="3">
         <v>7227000</v>
@@ -4875,22 +4873,22 @@
         <v>45473</v>
       </c>
       <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44377</v>
       </c>
       <c r="K80" s="2">
         <v>44196</v>
@@ -4936,26 +4934,26 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>636000</v>
-      </c>
-      <c r="E81" s="3">
-        <v>626000</v>
-      </c>
-      <c r="F81" s="3">
-        <v>790000</v>
-      </c>
-      <c r="G81" s="3">
-        <v>945000</v>
-      </c>
-      <c r="H81" s="3">
-        <v>1167000</v>
-      </c>
-      <c r="I81" s="3">
-        <v>304000</v>
-      </c>
-      <c r="J81" s="3">
-        <v>354000</v>
+      <c r="D81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K81" s="3">
         <v>-68000</v>
@@ -5027,25 +5025,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>475500</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>475500</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>447000</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>447000</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>426500</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>426500</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>314500</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -5417,25 +5415,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1476000</v>
+        <v>720000</v>
       </c>
       <c r="E89" s="3">
-        <v>1746000</v>
+        <v>720000</v>
       </c>
       <c r="F89" s="3">
-        <v>1554000</v>
+        <v>815000</v>
       </c>
       <c r="G89" s="3">
-        <v>2343000</v>
+        <v>815000</v>
       </c>
       <c r="H89" s="3">
-        <v>2137000</v>
+        <v>814000</v>
       </c>
       <c r="I89" s="3">
-        <v>1330000</v>
+        <v>814000</v>
       </c>
       <c r="J89" s="3">
-        <v>942000</v>
+        <v>1210500</v>
       </c>
       <c r="K89" s="3">
         <v>638000</v>
@@ -5507,25 +5505,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1173000</v>
+        <v>-586500</v>
       </c>
       <c r="E91" s="3">
-        <v>-1296000</v>
+        <v>-586500</v>
       </c>
       <c r="F91" s="3">
-        <v>-1073000</v>
+        <v>-648000</v>
       </c>
       <c r="G91" s="3">
-        <v>-929000</v>
+        <v>-648000</v>
       </c>
       <c r="H91" s="3">
-        <v>-778000</v>
+        <v>-536500</v>
       </c>
       <c r="I91" s="3">
-        <v>-611000</v>
+        <v>-536500</v>
       </c>
       <c r="J91" s="3">
-        <v>-492000</v>
+        <v>-464500</v>
       </c>
       <c r="K91" s="3">
         <v>-365000</v>
@@ -5702,25 +5700,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1396000</v>
+        <v>-698000</v>
       </c>
       <c r="E94" s="3">
-        <v>-1495000</v>
+        <v>-698000</v>
       </c>
       <c r="F94" s="3">
-        <v>-1401000</v>
+        <v>-747500</v>
       </c>
       <c r="G94" s="3">
-        <v>-1057000</v>
+        <v>-747500</v>
       </c>
       <c r="H94" s="3">
-        <v>-612000</v>
+        <v>-700500</v>
       </c>
       <c r="I94" s="3">
-        <v>197000</v>
+        <v>-700500</v>
       </c>
       <c r="J94" s="3">
-        <v>-334000</v>
+        <v>-528500</v>
       </c>
       <c r="K94" s="3">
         <v>-342000</v>
@@ -5792,25 +5790,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-568000</v>
+        <v>284000</v>
       </c>
       <c r="E96" s="3">
-        <v>-279000</v>
+        <v>284000</v>
       </c>
       <c r="F96" s="3">
-        <v>-498000</v>
+        <v>139500</v>
       </c>
       <c r="G96" s="3">
-        <v>-248000</v>
+        <v>139500</v>
       </c>
       <c r="H96" s="3">
-        <v>-288000</v>
+        <v>249000</v>
       </c>
       <c r="I96" s="3">
-        <v>-117000</v>
+        <v>249000</v>
       </c>
       <c r="J96" s="3">
-        <v>-104000</v>
+        <v>124000</v>
       </c>
       <c r="K96" s="3">
         <v>-44000</v>
@@ -6052,25 +6050,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-285000</v>
+        <v>-142500</v>
       </c>
       <c r="E100" s="3">
-        <v>-122000</v>
+        <v>-142500</v>
       </c>
       <c r="F100" s="3">
-        <v>-738000</v>
+        <v>-61000</v>
       </c>
       <c r="G100" s="3">
-        <v>-2272000</v>
+        <v>-61000</v>
       </c>
       <c r="H100" s="3">
-        <v>-1129000</v>
+        <v>-369000</v>
       </c>
       <c r="I100" s="3">
-        <v>-960000</v>
+        <v>-369000</v>
       </c>
       <c r="J100" s="3">
-        <v>479000</v>
+        <v>-1136000</v>
       </c>
       <c r="K100" s="3">
         <v>-255000</v>
@@ -6117,25 +6115,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="H101" s="3">
         <v>-11000</v>
       </c>
-      <c r="E101" s="3">
-        <v>-16000</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-12000</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-22000</v>
-      </c>
       <c r="I101" s="3">
-        <v>-8000</v>
+        <v>-11000</v>
       </c>
       <c r="J101" s="3">
-        <v>11000</v>
+        <v>-4000</v>
       </c>
       <c r="K101" s="3">
         <v>16000</v>
@@ -6182,25 +6180,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-216000</v>
+        <v>-126000</v>
       </c>
       <c r="E102" s="3">
-        <v>229000</v>
+        <v>-126000</v>
       </c>
       <c r="F102" s="3">
-        <v>-664000</v>
+        <v>-1500</v>
       </c>
       <c r="G102" s="3">
-        <v>-998000</v>
+        <v>-1500</v>
       </c>
       <c r="H102" s="3">
-        <v>374000</v>
+        <v>-258000</v>
       </c>
       <c r="I102" s="3">
-        <v>559000</v>
+        <v>-258000</v>
       </c>
       <c r="J102" s="3">
-        <v>1098000</v>
+        <v>-460000</v>
       </c>
       <c r="K102" s="3">
         <v>57000</v>

--- a/AAII_Financials/Quarterly/SSLZY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSLZY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="92">
   <si>
     <t>SSLZY</t>
   </si>
@@ -656,20 +656,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -680,85 +679,93 @@
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44196</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44012</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43830</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43646</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43465</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43281</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43100</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>42916</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>42735</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>42551</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>42369</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42185</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -783,47 +790,53 @@
       <c r="J8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M8" s="3">
         <v>1784000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1728000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>2143000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>2043000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2046000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1727000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1692000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1506000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1403000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1191000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1181000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1261000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>2150000</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -848,47 +861,53 @@
       <c r="J9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M9" s="3">
         <v>1398000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1245000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1457000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1241000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1149000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1162000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1253000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1066000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1069000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1055000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1001000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>882000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1570000</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -913,47 +932,53 @@
       <c r="J10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M10" s="3">
         <v>386000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>483000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>686000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>802000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>897000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>565000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>439000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>440000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>334000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>136000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>180000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>379000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>580000</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -977,8 +1002,10 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1003,47 +1030,53 @@
       <c r="J12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M12" s="3">
         <v>34000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>25000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>75000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>28000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>60000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>45000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>41000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>53000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>91000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>47000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>36000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>152000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>154000</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1107,8 +1140,14 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1133,47 +1172,53 @@
       <c r="J14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M14" s="3">
         <v>134000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>755000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>52000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>25000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>100000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>76000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>-34000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>951000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>44000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>1477000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>2854000</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>2289000</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1198,23 +1243,23 @@
       <c r="J15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M15" s="3">
         <v>1000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P15" s="3">
         <v>3000</v>
-      </c>
-      <c r="O15" s="3">
-        <v>1000</v>
-      </c>
-      <c r="P15" s="3">
-        <v>1000</v>
       </c>
       <c r="Q15" s="3">
         <v>1000</v>
@@ -1226,19 +1271,25 @@
         <v>1000</v>
       </c>
       <c r="T15" s="3">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="U15" s="3">
         <v>1000</v>
       </c>
       <c r="V15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="W15" s="3">
         <v>1000</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1259,8 +1310,10 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1285,47 +1338,53 @@
       <c r="J17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M17" s="3">
         <v>1699000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2119000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1715000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1453000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1275000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1392000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1535000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2248000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1286000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2793000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>3953000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1087000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3834000</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1350,47 +1409,53 @@
       <c r="J18" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M18" s="3">
         <v>85000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-391000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>428000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>590000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>771000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>335000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>157000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-742000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>117000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-1602000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-2772000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>174000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-1684000</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1414,8 +1479,10 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1440,11 +1507,11 @@
       <c r="J20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1479,8 +1546,14 @@
       <c r="W20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1505,47 +1578,53 @@
       <c r="J21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M21" s="3">
         <v>128000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>95000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>510000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1050000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>782000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>663000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>203000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-394000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="V21" s="3">
         <v>-1203000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-2731000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>550000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-1554000</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1570,11 +1649,11 @@
       <c r="J22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1609,8 +1688,14 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1635,47 +1720,53 @@
       <c r="J23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M23" s="3">
         <v>85000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-391000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>428000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>590000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>771000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>335000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>157000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-742000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>117000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-1602000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-2772000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>174000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-1684000</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1700,47 +1791,53 @@
       <c r="J24" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M24" s="3">
         <v>153000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-102000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>142000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>202000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>245000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>231000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>11000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-236000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>60000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-498000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-789000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>144000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-543000</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1804,8 +1901,14 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1830,47 +1933,53 @@
       <c r="J26" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M26" s="3">
         <v>-68000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-289000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>286000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>388000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>526000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>104000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>146000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-506000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>57000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-1104000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-1983000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>30000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1895,47 +2004,53 @@
       <c r="J27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M27" s="3">
         <v>-68000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-289000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>286000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>388000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>526000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>104000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>146000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-506000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>57000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-1104000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-1983000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>30000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1999,8 +2114,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2025,11 +2146,11 @@
       <c r="J29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2064,8 +2185,14 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2129,8 +2256,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2194,8 +2327,14 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2220,11 +2359,11 @@
       <c r="J32" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -2259,8 +2398,14 @@
       <c r="W32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2285,47 +2430,53 @@
       <c r="J33" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M33" s="3">
         <v>-68000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-289000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>286000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>388000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>526000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>104000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>146000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-506000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>57000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-1104000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-1983000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>30000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2389,8 +2540,14 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2415,117 +2572,129 @@
       <c r="J35" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M35" s="3">
         <v>-68000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-289000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>286000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>388000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>526000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>104000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>146000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-506000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>57000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-1104000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-1983000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>30000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44196</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44012</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43830</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43646</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43465</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43281</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43100</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>42916</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>42735</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>42551</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>42369</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42185</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2549,8 +2718,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2574,73 +2745,81 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1833000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1833000</v>
+      </c>
+      <c r="F41" s="3">
         <v>1659000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1659000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1875000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1875000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1840000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1840000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2352000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1319000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1262000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1067000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1215000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1316000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1492000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1231000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>2226000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>2026000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1034000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1343000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>399000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>775000</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2651,495 +2830,537 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>252000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>252000</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>55000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>29000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>25000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>195000</v>
-      </c>
-      <c r="N42" s="3">
-        <v>14000</v>
-      </c>
-      <c r="O42" s="3">
-        <v>28000</v>
       </c>
       <c r="P42" s="3">
         <v>14000</v>
       </c>
       <c r="Q42" s="3">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="R42" s="3">
+        <v>14000</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
         <v>17000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>7000</v>
-      </c>
-      <c r="T42" s="3">
-        <v>1000</v>
-      </c>
-      <c r="U42" s="3">
-        <v>651000</v>
       </c>
       <c r="V42" s="3">
         <v>1000</v>
       </c>
       <c r="W42" s="3">
+        <v>651000</v>
+      </c>
+      <c r="X42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y42" s="3">
         <v>66000</v>
       </c>
     </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>843000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>843000</v>
+      </c>
+      <c r="F43" s="3">
         <v>892000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>892000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>932000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>932000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>810000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>810000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>879000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>583000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>540000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>577000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>423000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>562000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>451000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>447000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>370000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>382000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>532000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>477000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>650000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>690000</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>428000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>428000</v>
+      </c>
+      <c r="F44" s="3">
         <v>418000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>418000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>442000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>442000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>455000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>455000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>443000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>288000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>284000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>301000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>304000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>288000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>252000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>266000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>284000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>321000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>379000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>360000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>526000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>443000</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F45" s="3">
         <v>80000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>80000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>752000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>752000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1392000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1392000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1329000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>477000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>25000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>40000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>10000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>32000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>293000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>28000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>32000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>214000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>45000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>448000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>86000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>91000</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3186000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3186000</v>
+      </c>
+      <c r="F46" s="3">
         <v>3103000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3103000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4347000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4347000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>4527000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>4527000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>5128000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2696000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2136000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>2180000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1966000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>2226000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>2502000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1972000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>2929000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>2950000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1991000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>2125000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1662000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>2065000</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>393000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>393000</v>
+      </c>
+      <c r="F47" s="3">
         <v>415000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>415000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>406000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>406000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>400000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>400000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>379000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>543000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>959000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>172000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>157000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>219000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>82000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>177000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>197000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>213000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>233000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>233000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>287000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>273000</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23112000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>23112000</v>
+      </c>
+      <c r="F48" s="3">
         <v>22978000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>22978000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>21972000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>21972000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>20627000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>20627000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>20494000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>12991000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>12796000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>12806000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>12715000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>12383000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>9673000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>10121000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>10169000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>11028000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>11710000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>13105000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>21096000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>19795000</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1265000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1265000</v>
+      </c>
+      <c r="F49" s="3">
         <v>1319000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1319000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1251000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1251000</v>
-      </c>
-      <c r="H49" s="3">
-        <v>1190000</v>
-      </c>
-      <c r="I49" s="3">
-        <v>1190000</v>
       </c>
       <c r="J49" s="3">
         <v>1190000</v>
       </c>
       <c r="K49" s="3">
+        <v>1190000</v>
+      </c>
+      <c r="L49" s="3">
+        <v>1190000</v>
+      </c>
+      <c r="M49" s="3">
         <v>383000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>481000</v>
-      </c>
-      <c r="M49" s="3">
-        <v>481000</v>
-      </c>
-      <c r="N49" s="3">
-        <v>628000</v>
       </c>
       <c r="O49" s="3">
         <v>481000</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>11</v>
+      <c r="P49" s="3">
+        <v>628000</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>481000</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>11</v>
@@ -3153,14 +3374,20 @@
       <c r="U49" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
-      </c>
-      <c r="W49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="W49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3224,8 +3451,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3289,73 +3522,85 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>568000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>568000</v>
+      </c>
+      <c r="F52" s="3">
         <v>637000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>637000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>502000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>502000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>423000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>423000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>299000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1043000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1083000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>870000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1761000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1502000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1154000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>1436000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1377000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1071000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1089000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>486000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>468000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>212000</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3419,73 +3664,85 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>29633000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>29633000</v>
+      </c>
+      <c r="F54" s="3">
         <v>29550000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>29550000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>29756000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>29756000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>28479000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>28479000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>28856000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>17656000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>17455000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>16509000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>17227000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>16811000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>13411000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>13706000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>14672000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>15262000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>15023000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>15949000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>23513000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>22345000</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3509,8 +3766,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3534,398 +3793,436 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>459000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>459000</v>
+      </c>
+      <c r="F57" s="3">
         <v>973000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>973000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>567000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>567000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>807000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>807000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>805000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>558000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>549000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>719000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>556000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>661000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>455000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>495000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>474000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>520000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>483000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>618000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>952000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1382000</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>887000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>887000</v>
+      </c>
+      <c r="F58" s="3">
         <v>981000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>981000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>835000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>835000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>877000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>877000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>938000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>354000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>336000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>310000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>435000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>967000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>803000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>207000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>415000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>420000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>190000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>152000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>400000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>979000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>979000</v>
+      </c>
+      <c r="F59" s="3">
         <v>830000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>830000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1441000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1441000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1228000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1228000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1613000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>623000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>241000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>290000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>233000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>226000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>485000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>249000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>370000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>616000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>202000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>156000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>226000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>237000</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2413000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2413000</v>
+      </c>
+      <c r="F60" s="3">
         <v>2784000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2784000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2948000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2948000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2912000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2912000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3472000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1535000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1126000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1319000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1224000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1854000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1743000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>951000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1259000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1556000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>875000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>926000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1578000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1946000</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5801000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>5801000</v>
+      </c>
+      <c r="F61" s="3">
         <v>5494000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>5494000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>5324000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>5324000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>4856000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>4856000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>4581000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>4645000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>4722000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>4111000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>4175000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>3952000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>3026000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>3756000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>4588000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>4842000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>5491000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>5555000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>8953000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>8106000</v>
       </c>
     </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3922000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3922000</v>
+      </c>
+      <c r="F62" s="3">
         <v>3646000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>3646000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>4152000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>4152000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>3875000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>3875000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>3822000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>4249000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>4309000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>3403000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>4296000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>3726000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1644000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>1848000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1908000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1784000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>2288000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2047000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>3269000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>2880000</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3989,8 +4286,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4054,8 +4357,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4119,73 +4428,85 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14096000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>14096000</v>
+      </c>
+      <c r="F66" s="3">
         <v>13907000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>13907000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>14481000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>14481000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>13674000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>13674000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>14013000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>10429000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>10157000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>8833000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>9695000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>9532000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>6413000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>6555000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>7755000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>8182000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>8654000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>8528000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>13800000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>12928000</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4209,8 +4530,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4274,8 +4597,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4339,8 +4668,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4404,8 +4739,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4469,73 +4810,85 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2240000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2240000</v>
+      </c>
+      <c r="F72" s="3">
         <v>2064000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>2064000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>1792000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1792000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1437000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1437000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1153000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-865000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-758000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-359000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-514000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-774000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-1230000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-1339000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-1487000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-980000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-1045000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>122000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>2070000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>2166000</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4599,8 +4952,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4664,8 +5023,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4729,73 +5094,85 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15537000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>15537000</v>
+      </c>
+      <c r="F76" s="3">
         <v>15444000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>15444000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>15275000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>15275000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>14805000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>14805000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>14843000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>7227000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>7298000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>7676000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>7532000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>7279000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>6998000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>7151000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>6917000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>7080000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>6369000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>7421000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>9713000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>9417000</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4859,78 +5236,90 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44196</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44012</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43830</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43646</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43465</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43281</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43100</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>42916</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>42735</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>42551</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>42369</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42185</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4955,47 +5344,53 @@
       <c r="J81" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M81" s="3">
         <v>-68000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-289000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>286000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>388000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>526000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>104000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>146000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-506000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>57000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-1104000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-1983000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>30000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5019,38 +5414,40 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>453500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>453500</v>
+      </c>
+      <c r="F83" s="3">
         <v>475500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>475500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>447000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>447000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>426500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>426500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>314500</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
@@ -5084,8 +5481,14 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5149,8 +5552,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5214,8 +5623,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5279,8 +5694,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5344,8 +5765,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5409,73 +5836,85 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>705000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>705000</v>
+      </c>
+      <c r="F89" s="3">
         <v>720000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>720000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>815000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>815000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>814000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>814000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1210500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>638000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>838000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>995000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1051000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>934000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>644000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>586000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>662000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>566000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>291000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>562000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>532000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>1099000</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5499,73 +5938,81 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-614000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-614000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-586500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-586500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-648000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-648000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-536500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-536500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-464500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-365000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1100000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-490000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-5000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-7000</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-2000</v>
       </c>
       <c r="R91" s="3">
         <v>-3000</v>
       </c>
       <c r="S91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="T91" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="U91" s="3">
         <v>3000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-7000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-11000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-2211000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-1694000</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5629,8 +6076,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5694,73 +6147,85 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-644500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-644500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-698000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-698000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-747500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-747500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-700500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-700500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-528500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-342000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1119000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-674000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-359000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-2115000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-258000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-312000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-222000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-225000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>20000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-600000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-992000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-1799000</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5784,50 +6249,52 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>211500</v>
+      </c>
+      <c r="E96" s="3">
+        <v>211500</v>
+      </c>
+      <c r="F96" s="3">
         <v>284000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>284000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>139500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>139500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>249000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>249000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>124000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-44000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-92000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-124000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-127000</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -5838,19 +6305,25 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-43000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-78000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-83000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-115000</v>
       </c>
     </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5914,8 +6387,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5979,8 +6458,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6044,199 +6529,223 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>39500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-142500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-142500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-61000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-61000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-369000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-369000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1136000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-255000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>501000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-460000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-791000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>1010000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-120000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-1298000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-220000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>664000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-121000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>1033000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>333000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>1016000</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-2500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-2500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-6000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-6000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-11000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-11000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-4000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>16000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-25000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-9000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-2000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-5000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>7000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>2000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>4000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>5000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-2000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>23000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>87000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>87000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-126000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-126000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-258000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-258000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-460000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>57000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>195000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-148000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-101000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-176000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>261000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-995000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>200000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>992000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>195000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>707000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-328000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>327000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SSLZY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSLZY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="92">
   <si>
     <t>SSLZY</t>
   </si>
@@ -656,23 +656,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -683,97 +682,105 @@
     <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43646</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43465</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43281</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43100</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42916</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>42735</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42551</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42369</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42185</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -810,47 +817,53 @@
       <c r="N8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q8" s="3">
         <v>1784000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1728000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>2143000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>2043000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>2046000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1727000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1692000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1506000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1403000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1191000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1181000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>1261000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>2150000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -887,47 +900,53 @@
       <c r="N9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q9" s="3">
         <v>1398000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1245000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1457000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1241000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1149000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1162000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1253000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1066000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1069000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1055000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1001000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>882000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>1570000</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -964,47 +983,53 @@
       <c r="N10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q10" s="3">
         <v>386000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>483000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>686000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>802000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>897000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>565000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>439000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>440000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>334000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>136000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>180000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>379000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>580000</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1032,8 +1057,10 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1070,47 +1097,53 @@
       <c r="N12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q12" s="3">
         <v>34000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>25000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>75000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>28000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>60000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>45000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>41000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>53000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>91000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>47000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>36000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>152000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>154000</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1186,8 +1219,14 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1224,47 +1263,53 @@
       <c r="N14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q14" s="3">
         <v>134000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>755000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>52000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>25000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>100000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>76000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>-34000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>951000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>44000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>1477000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>2854000</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>2289000</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1301,23 +1346,23 @@
       <c r="N15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q15" s="3">
         <v>1000</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="T15" s="3">
         <v>3000</v>
-      </c>
-      <c r="S15" s="3">
-        <v>1000</v>
-      </c>
-      <c r="T15" s="3">
-        <v>1000</v>
       </c>
       <c r="U15" s="3">
         <v>1000</v>
@@ -1329,19 +1374,25 @@
         <v>1000</v>
       </c>
       <c r="X15" s="3">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="Y15" s="3">
         <v>1000</v>
       </c>
       <c r="Z15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AA15" s="3">
         <v>1000</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AC15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1366,8 +1417,10 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1404,47 +1457,53 @@
       <c r="N17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q17" s="3">
         <v>1699000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2119000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1715000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1453000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1275000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1392000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1535000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2248000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1286000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>2793000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>3953000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>1087000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>3834000</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1481,47 +1540,53 @@
       <c r="N18" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q18" s="3">
         <v>85000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-391000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>428000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>590000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>771000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>335000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>157000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-742000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>117000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-1602000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-2772000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>174000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-1684000</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1549,8 +1614,10 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1587,11 +1654,11 @@
       <c r="N20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -1626,8 +1693,14 @@
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1664,47 +1737,53 @@
       <c r="N21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q21" s="3">
         <v>128000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>95000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>510000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1050000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>782000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>663000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>203000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-394000</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-1203000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-2731000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>550000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-1554000</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1741,11 +1820,11 @@
       <c r="N22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1780,8 +1859,14 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1818,47 +1903,53 @@
       <c r="N23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q23" s="3">
         <v>85000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-391000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>428000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>590000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>771000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>335000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>157000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-742000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>117000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-1602000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-2772000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>174000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-1684000</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1895,47 +1986,53 @@
       <c r="N24" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q24" s="3">
         <v>153000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-102000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>142000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>202000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>245000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>231000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>11000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-236000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>60000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-498000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-789000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>144000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-543000</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2011,8 +2108,14 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2049,47 +2152,53 @@
       <c r="N26" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-68000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-289000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>286000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>388000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>526000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>104000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>146000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-506000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>57000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-1104000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-1983000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>30000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2126,47 +2235,53 @@
       <c r="N27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-68000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-289000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>286000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>388000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>526000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>104000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>146000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-506000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>57000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-1104000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-1983000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>30000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2242,8 +2357,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2280,11 +2401,11 @@
       <c r="N29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -2319,8 +2440,14 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2396,8 +2523,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2473,8 +2606,14 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2511,11 +2650,11 @@
       <c r="N32" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -2550,8 +2689,14 @@
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2588,47 +2733,53 @@
       <c r="N33" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-68000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-289000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>286000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>388000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>526000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>104000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>146000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-506000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>57000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-1104000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-1983000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>30000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2704,8 +2855,14 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2742,129 +2899,141 @@
       <c r="N35" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-68000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-289000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>286000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>388000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>526000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>104000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>146000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-506000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>57000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-1104000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-1983000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>30000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43646</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43465</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43281</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43100</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42916</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>42735</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42551</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42369</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42185</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2892,8 +3061,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2921,85 +3092,93 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1722000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1722000</v>
+      </c>
+      <c r="F41" s="3">
         <v>1830000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1830000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1833000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1833000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1659000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1659000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1875000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1875000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1840000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1840000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2352000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1319000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1262000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1067000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1215000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1316000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1492000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1231000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>2226000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>2026000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1034000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1343000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>399000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>775000</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3022,579 +3201,621 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>252000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>252000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>55000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>29000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>25000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>195000</v>
-      </c>
-      <c r="R42" s="3">
-        <v>14000</v>
-      </c>
-      <c r="S42" s="3">
-        <v>28000</v>
       </c>
       <c r="T42" s="3">
         <v>14000</v>
       </c>
       <c r="U42" s="3">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="V42" s="3">
+        <v>14000</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
         <v>17000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>7000</v>
-      </c>
-      <c r="X42" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Y42" s="3">
-        <v>651000</v>
       </c>
       <c r="Z42" s="3">
         <v>1000</v>
       </c>
       <c r="AA42" s="3">
+        <v>651000</v>
+      </c>
+      <c r="AB42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AC42" s="3">
         <v>66000</v>
       </c>
     </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>741000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>741000</v>
+      </c>
+      <c r="F43" s="3">
         <v>707000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>707000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>843000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>843000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>892000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>892000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>932000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>932000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>810000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>810000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>879000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>583000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>540000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>577000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>423000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>562000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>451000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>447000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>370000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>382000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>532000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>477000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>650000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>690000</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>386000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>386000</v>
+      </c>
+      <c r="F44" s="3">
         <v>415000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>415000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>428000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>428000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>418000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>418000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>442000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>442000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>455000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>455000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>443000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>288000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>284000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>301000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>304000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>288000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>252000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>266000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>284000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>321000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>379000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>360000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>526000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>443000</v>
       </c>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>48000</v>
+      </c>
+      <c r="F45" s="3">
         <v>62000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>62000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>5000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>5000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>80000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>80000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>752000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>752000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1392000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1392000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1329000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>477000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>25000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>40000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>10000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>32000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>293000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>28000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>32000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>214000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>45000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>448000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>86000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>91000</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2957000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2957000</v>
+      </c>
+      <c r="F46" s="3">
         <v>3064000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3064000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3186000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3186000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3103000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>3103000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>4347000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>4347000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>4527000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>4527000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>5128000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>2696000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>2136000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2180000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1966000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>2226000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>2502000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1972000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>2929000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>2950000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1991000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>2125000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>1662000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>2065000</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>369000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>369000</v>
+      </c>
+      <c r="F47" s="3">
         <v>391000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>391000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>393000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>393000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>415000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>415000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>406000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>406000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>400000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>400000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>379000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>543000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>959000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>172000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>157000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>219000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>82000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>177000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>197000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>213000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>233000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>233000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>287000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>273000</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24674000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>24674000</v>
+      </c>
+      <c r="F48" s="3">
         <v>23400000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>23400000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>23112000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>23112000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>22978000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>22978000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>21972000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>21972000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>20627000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>20627000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>20494000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>12991000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>12796000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>12806000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>12715000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>12383000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>9673000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>10121000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>10169000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>11028000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>11710000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>13105000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>21096000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>19795000</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1309000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1309000</v>
+      </c>
+      <c r="F49" s="3">
         <v>1263000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1263000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1265000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1265000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1319000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1319000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1251000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1251000</v>
-      </c>
-      <c r="L49" s="3">
-        <v>1190000</v>
-      </c>
-      <c r="M49" s="3">
-        <v>1190000</v>
       </c>
       <c r="N49" s="3">
         <v>1190000</v>
       </c>
       <c r="O49" s="3">
+        <v>1190000</v>
+      </c>
+      <c r="P49" s="3">
+        <v>1190000</v>
+      </c>
+      <c r="Q49" s="3">
         <v>383000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>481000</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>481000</v>
-      </c>
-      <c r="R49" s="3">
-        <v>628000</v>
       </c>
       <c r="S49" s="3">
         <v>481000</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="U49" s="3" t="s">
-        <v>11</v>
+      <c r="T49" s="3">
+        <v>628000</v>
+      </c>
+      <c r="U49" s="3">
+        <v>481000</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>11</v>
@@ -3608,14 +3829,20 @@
       <c r="Y49" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3691,8 +3918,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3768,85 +4001,97 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>63000</v>
+      </c>
+      <c r="F52" s="3">
         <v>655000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>655000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>568000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>568000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>637000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>637000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>502000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>502000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>423000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>423000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>299000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1043000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1083000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>870000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1761000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1502000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1154000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>1436000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1377000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>1071000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1089000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>486000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>468000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>212000</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3922,85 +4167,97 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>30530000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>30530000</v>
+      </c>
+      <c r="F54" s="3">
         <v>29878000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>29878000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>29633000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>29633000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>29550000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>29550000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>29756000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>29756000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>28479000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>28479000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>28856000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>17656000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>17455000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>16509000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>17227000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>16811000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>13411000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>13706000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>14672000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>15262000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>15023000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>15949000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>23513000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>22345000</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4028,8 +4285,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4057,470 +4316,508 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>400000</v>
+      </c>
+      <c r="F57" s="3">
         <v>818000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>818000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>459000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>459000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>973000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>973000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>567000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>567000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>807000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>807000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>805000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>558000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>549000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>719000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>556000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>661000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>455000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>495000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>474000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>520000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>483000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>618000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>952000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>1382000</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>264000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>264000</v>
+      </c>
+      <c r="F58" s="3">
         <v>925000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>925000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>887000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>887000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>981000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>981000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>835000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>835000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>877000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>877000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>938000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>354000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>336000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>310000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>435000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>967000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>803000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>207000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>415000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>420000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>190000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>152000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>400000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1186000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1186000</v>
+      </c>
+      <c r="F59" s="3">
         <v>673000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>673000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>979000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>979000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>830000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>830000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1441000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1441000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1228000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1228000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1613000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>623000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>241000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>290000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>233000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>226000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>485000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>249000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>370000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>616000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>202000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>156000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>226000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>237000</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1938000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1938000</v>
+      </c>
+      <c r="F60" s="3">
         <v>2416000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2416000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2413000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2413000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2784000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2784000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2948000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2948000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2912000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2912000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3472000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1535000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1126000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1319000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1224000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1854000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1743000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>951000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1259000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1556000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>875000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>926000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1578000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>1946000</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7276000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>7276000</v>
+      </c>
+      <c r="F61" s="3">
         <v>5864000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>5864000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>5801000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>5801000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>5494000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>5494000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>5324000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>5324000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>4856000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>4856000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>4581000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>4645000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>4722000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>4111000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>4175000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>3952000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>3026000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>3756000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>4588000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>4842000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>5491000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>5555000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>8953000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>8106000</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3841000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3841000</v>
+      </c>
+      <c r="F62" s="3">
         <v>4025000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>4025000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>3922000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>3922000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>3646000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>3646000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>4152000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>4152000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>3875000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>3875000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>3822000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>4249000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>4309000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3403000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>4296000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>3726000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1644000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1848000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1908000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>1784000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>2288000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>2047000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>3269000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>2880000</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4596,8 +4893,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4673,8 +4976,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4750,85 +5059,97 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14865000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>14865000</v>
+      </c>
+      <c r="F66" s="3">
         <v>14166000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>14166000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>14096000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>14096000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>13907000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>13907000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>14481000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>14481000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>13674000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>13674000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>14013000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>10429000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>10157000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>8833000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>9695000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>9532000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>6413000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>6555000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>7755000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>8182000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>8654000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>8528000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>13800000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>12928000</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4856,8 +5177,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4933,8 +5256,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5010,8 +5339,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5087,8 +5422,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5164,85 +5505,97 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2283000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2283000</v>
+      </c>
+      <c r="F72" s="3">
         <v>2335000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>2335000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>2240000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>2240000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>2064000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>2064000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1792000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1792000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1437000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1437000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>1153000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-865000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-758000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-359000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-514000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-774000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-1230000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-1339000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-1487000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-980000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-1045000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>122000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>2070000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>2166000</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5318,8 +5671,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5395,8 +5754,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5472,85 +5837,97 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15665000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>15665000</v>
+      </c>
+      <c r="F76" s="3">
         <v>15712000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>15712000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>15537000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>15537000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>15444000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>15444000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>15275000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>15275000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>14805000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>14805000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>14843000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>7227000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>7298000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>7676000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>7532000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>7279000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>6998000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>7151000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>6917000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>7080000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>6369000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>7421000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>9713000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>9417000</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5626,90 +6003,102 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43646</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43465</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43281</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43100</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42916</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>42735</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42551</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42369</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42185</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5746,47 +6135,53 @@
       <c r="N81" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-68000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-289000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>286000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>388000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>526000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>104000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>146000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-506000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>57000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-1104000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-1983000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>30000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5814,50 +6209,52 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>417000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>417000</v>
+      </c>
+      <c r="F83" s="3">
         <v>422500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>422500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>453500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>453500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>475500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>475500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>447000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>447000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>426500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>426500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>314500</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
@@ -5891,8 +6288,14 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5968,8 +6371,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6045,8 +6454,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6122,8 +6537,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6199,8 +6620,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6276,85 +6703,97 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>630500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>630500</v>
+      </c>
+      <c r="F89" s="3">
         <v>776000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>776000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>705000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>705000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>720000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>720000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>815000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>815000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>814000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>814000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1210500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>638000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>838000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>995000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>1051000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>934000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>644000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>586000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>662000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>566000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>291000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>562000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>532000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>1099000</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6382,85 +6821,93 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-508000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-508000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-520000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-520000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-614000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-614000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-586500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-586500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-648000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-648000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-536500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-536500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-464500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-365000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1100000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-490000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-5000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-7000</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-2000</v>
       </c>
       <c r="V91" s="3">
         <v>-3000</v>
       </c>
       <c r="W91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="X91" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Y91" s="3">
         <v>3000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-2211000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-1694000</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6536,8 +6983,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6613,85 +7066,97 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-497500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-497500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-591500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-591500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-644500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-644500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-698000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-698000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-747500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-747500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-700500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-700500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-528500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-342000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1119000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-674000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-359000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-2115000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-258000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-312000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-222000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-225000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>20000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-600000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-992000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-1799000</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6719,62 +7184,64 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>217500</v>
+      </c>
+      <c r="E96" s="3">
+        <v>217500</v>
+      </c>
+      <c r="F96" s="3">
         <v>167500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>167500</v>
       </c>
-      <c r="F96" s="3">
-        <v>211500</v>
-      </c>
-      <c r="G96" s="3">
-        <v>211500</v>
-      </c>
       <c r="H96" s="3">
+        <v>211000</v>
+      </c>
+      <c r="I96" s="3">
+        <v>211000</v>
+      </c>
+      <c r="J96" s="3">
         <v>284500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>284500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>139500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>139500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>249000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>249000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>124000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-44000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-92000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-124000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-127000</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -6785,19 +7252,25 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-43000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-78000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-83000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-115000</v>
       </c>
     </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6873,8 +7346,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6950,8 +7429,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7027,235 +7512,259 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-202500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-202500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-193000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-193000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>39500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>39500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-142500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-142500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-61000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-61000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-369000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-369000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1136000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-255000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>501000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-460000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-791000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>1010000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-120000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-1298000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-220000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>664000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-121000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>1033000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>333000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>1016000</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-5500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-5500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-8000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-8000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-2500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-2500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-6000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-6000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-11000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-11000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-4000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>16000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-25000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-9000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-2000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-5000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-5000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>7000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>4000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>5000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>23000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>87000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>87000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-126000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-126000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-258000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-258000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-460000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>57000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>195000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-148000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-101000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-176000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>261000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-995000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>200000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>992000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>195000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>707000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-328000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>327000</v>
       </c>
     </row>
